--- a/artfynd/A 19225-2025 artfynd.xlsx
+++ b/artfynd/A 19225-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>126719461</v>
       </c>
       <c r="B6" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>126719371</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>126721039</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>126719861</v>
       </c>
       <c r="B13" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 19225-2025 artfynd.xlsx
+++ b/artfynd/A 19225-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>126719461</v>
       </c>
       <c r="B6" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>126719371</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>126721039</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>126719861</v>
       </c>
       <c r="B13" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 19225-2025 artfynd.xlsx
+++ b/artfynd/A 19225-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>126719461</v>
       </c>
       <c r="B6" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>126719371</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>126721039</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>126719861</v>
       </c>
       <c r="B13" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 19225-2025 artfynd.xlsx
+++ b/artfynd/A 19225-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126719200</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126720940</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126719031</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126720622</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>126720233</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>126718950</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>126719512</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>126718741</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>126718834</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19225-2025 artfynd.xlsx
+++ b/artfynd/A 19225-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126719200</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126720940</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126719031</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126720622</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>126720233</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>126718950</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>126719512</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>126718741</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>126718834</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19225-2025 artfynd.xlsx
+++ b/artfynd/A 19225-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>126719461</v>
       </c>
       <c r="B6" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>126719371</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>126721039</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>126719861</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 19225-2025 artfynd.xlsx
+++ b/artfynd/A 19225-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126719200</v>
+        <v>126718741</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599127</v>
+        <v>599119</v>
       </c>
       <c r="R2" t="n">
-        <v>6924105</v>
+        <v>6924222</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126720940</v>
+        <v>126718834</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599194</v>
+        <v>599103</v>
       </c>
       <c r="R3" t="n">
-        <v>6924105</v>
+        <v>6924201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Flera äldre spår men tittar man noga ser man även två färska spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126719031</v>
+        <v>126718950</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599137</v>
+        <v>599114</v>
       </c>
       <c r="R4" t="n">
-        <v>6924106</v>
+        <v>6924165</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126720622</v>
+        <v>126719031</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599177</v>
+        <v>599137</v>
       </c>
       <c r="R5" t="n">
-        <v>6924075</v>
+        <v>6924106</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,45 +1103,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126719461</v>
+        <v>126719200</v>
       </c>
       <c r="B6" t="n">
-        <v>98360</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bäckegrensslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599181</v>
+        <v>599127</v>
       </c>
       <c r="R6" t="n">
-        <v>6924019</v>
+        <v>6924105</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126720233</v>
+        <v>126719512</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599205</v>
+        <v>599162</v>
       </c>
       <c r="R7" t="n">
-        <v>6924077</v>
+        <v>6924012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,45 +1317,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126719371</v>
+        <v>126720233</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bäckegrensslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599154</v>
+        <v>599205</v>
       </c>
       <c r="R8" t="n">
-        <v>6924041</v>
+        <v>6924077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,37 +1424,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126721039</v>
+        <v>126720622</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1443,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599186</v>
+        <v>599177</v>
       </c>
       <c r="R9" t="n">
-        <v>6924137</v>
+        <v>6924075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126718950</v>
+        <v>126720940</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,7 +1562,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1545,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599114</v>
+        <v>599194</v>
       </c>
       <c r="R10" t="n">
-        <v>6924165</v>
+        <v>6924105</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.  Flera äldre spår men tittar man noga ser man även två färska spår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,50 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126719512</v>
+        <v>126719371</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bäckegrensslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599162</v>
+        <v>599154</v>
       </c>
       <c r="R11" t="n">
-        <v>6924012</v>
+        <v>6924041</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,50 +1735,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126718741</v>
+        <v>126719461</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bäckegrensslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599119</v>
+        <v>599181</v>
       </c>
       <c r="R12" t="n">
-        <v>6924222</v>
+        <v>6924019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,7 +1835,7 @@
         <v>126719861</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,38 +1929,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126718834</v>
+        <v>126721039</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1963,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599103</v>
+        <v>599186</v>
       </c>
       <c r="R14" t="n">
-        <v>6924201</v>
+        <v>6924137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,11 +2004,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 19225-2025 artfynd.xlsx
+++ b/artfynd/A 19225-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126718741</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126718834</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126718950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126719031</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126719200</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126719512</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720233</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720622</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720940</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126719371</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126719461</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126719861</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,8 +2092,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721039</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>